--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260818.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260818.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>61,487,416</t>
+          <t>544,842,765</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>544,842,765</t>
+          <t>61,487,416</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>71,937,649</t>
+          <t>70,245,150</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>70,245,150</t>
+          <t>71,937,649</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,993,525</t>
+          <t>17,732,868</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>17,732,868</t>
+          <t>7,993,525</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
